--- a/datasets/sheet2.xlsx
+++ b/datasets/sheet2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="97">
   <si>
     <t>종목명</t>
   </si>
@@ -193,6 +193,12 @@
     <t>2000</t>
   </si>
   <si>
+    <t>15300</t>
+  </si>
+  <si>
+    <t>16000</t>
+  </si>
+  <si>
     <t>13000</t>
   </si>
   <si>
@@ -208,9 +214,6 @@
     <t>21000</t>
   </si>
   <si>
-    <t>16000</t>
-  </si>
-  <si>
     <t>10000</t>
   </si>
   <si>
@@ -232,7 +235,10 @@
     <t>78720</t>
   </si>
   <si>
-    <t>21308</t>
+    <t>23972</t>
+  </si>
+  <si>
+    <t>24000</t>
   </si>
   <si>
     <t>21700</t>
@@ -693,10 +699,10 @@
         <v>57</v>
       </c>
       <c r="E2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -716,7 +722,7 @@
         <v>57</v>
       </c>
       <c r="F3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -733,10 +739,10 @@
         <v>57</v>
       </c>
       <c r="E4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -753,10 +759,10 @@
         <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -773,10 +779,10 @@
         <v>57</v>
       </c>
       <c r="E6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -793,10 +799,10 @@
         <v>58</v>
       </c>
       <c r="E7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -810,13 +816,13 @@
         <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -830,13 +836,13 @@
         <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="F9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -850,13 +856,13 @@
         <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -870,13 +876,13 @@
         <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -890,13 +896,13 @@
         <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -913,10 +919,10 @@
         <v>58</v>
       </c>
       <c r="E13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -930,13 +936,13 @@
         <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -950,13 +956,13 @@
         <v>43</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -970,13 +976,13 @@
         <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -990,13 +996,13 @@
         <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1010,13 +1016,13 @@
         <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F18" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1033,10 +1039,10 @@
         <v>58</v>
       </c>
       <c r="E19" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1053,10 +1059,10 @@
         <v>58</v>
       </c>
       <c r="E20" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F20" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1070,13 +1076,13 @@
         <v>56</v>
       </c>
       <c r="D21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E21" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F21" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet2.xlsx
+++ b/datasets/sheet2.xlsx
@@ -34,15 +34,15 @@
     <t>주간사</t>
   </si>
   <si>
+    <t>아이언디바이스</t>
+  </si>
+  <si>
     <t>에이치이엠파마(구.에이치이엠)</t>
   </si>
   <si>
     <t>미래에셋비전스팩7호</t>
   </si>
   <si>
-    <t>아이언디바이스</t>
-  </si>
-  <si>
     <t>키움스팩9호</t>
   </si>
   <si>
@@ -94,15 +94,15 @@
     <t>산일전기(유가)</t>
   </si>
   <si>
+    <t>2024.08.30~09.05</t>
+  </si>
+  <si>
     <t>2024.08.26~08.30</t>
   </si>
   <si>
     <t>2024.08.26~08.27</t>
   </si>
   <si>
-    <t>2024.08.19~08.23</t>
-  </si>
-  <si>
     <t>2024.08.13~08.14</t>
   </si>
   <si>
@@ -145,15 +145,15 @@
     <t>2024.07.09~07.15</t>
   </si>
   <si>
+    <t>4,900~5,700</t>
+  </si>
+  <si>
     <t>18,000~21,000</t>
   </si>
   <si>
     <t>2,000~2,000</t>
   </si>
   <si>
-    <t>4,900~5,700</t>
-  </si>
-  <si>
     <t>32,000~40,200</t>
   </si>
   <si>
@@ -223,12 +223,12 @@
     <t>35000</t>
   </si>
   <si>
+    <t>14700</t>
+  </si>
+  <si>
     <t>12546</t>
   </si>
   <si>
-    <t>14700</t>
-  </si>
-  <si>
     <t>6000</t>
   </si>
   <si>
@@ -271,13 +271,13 @@
     <t>266000</t>
   </si>
   <si>
+    <t>대신증권</t>
+  </si>
+  <si>
     <t>신한투자증권</t>
   </si>
   <si>
     <t>미래에셋증권</t>
-  </si>
-  <si>
-    <t>대신증권</t>
   </si>
   <si>
     <t>키움증권</t>
@@ -719,7 +719,7 @@
         <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="F3" t="s">
         <v>86</v>
@@ -739,7 +739,7 @@
         <v>57</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F4" t="s">
         <v>87</v>
@@ -753,7 +753,7 @@
         <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
         <v>57</v>
@@ -793,7 +793,7 @@
         <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
         <v>58</v>
@@ -802,7 +802,7 @@
         <v>61</v>
       </c>
       <c r="F7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -902,7 +902,7 @@
         <v>76</v>
       </c>
       <c r="F12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -913,7 +913,7 @@
         <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
         <v>58</v>
@@ -953,7 +953,7 @@
         <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
         <v>65</v>
@@ -982,7 +982,7 @@
         <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1033,7 +1033,7 @@
         <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D19" t="s">
         <v>58</v>
@@ -1053,7 +1053,7 @@
         <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D20" t="s">
         <v>58</v>

--- a/datasets/sheet2.xlsx
+++ b/datasets/sheet2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="95">
   <si>
     <t>종목명</t>
   </si>
@@ -49,6 +49,9 @@
     <t>제닉스</t>
   </si>
   <si>
+    <t>셀비온</t>
+  </si>
+  <si>
     <t>키움스팩9호</t>
   </si>
   <si>
@@ -91,9 +94,6 @@
     <t>넥스트바이오메디컬</t>
   </si>
   <si>
-    <t>유라클</t>
-  </si>
-  <si>
     <t>2024.09.09~09.13</t>
   </si>
   <si>
@@ -160,6 +160,9 @@
     <t>28,000~34,000</t>
   </si>
   <si>
+    <t>10,000~12,200</t>
+  </si>
+  <si>
     <t>8,000~10,000</t>
   </si>
   <si>
@@ -217,9 +220,6 @@
     <t>29000</t>
   </si>
   <si>
-    <t>21000</t>
-  </si>
-  <si>
     <t>49500</t>
   </si>
   <si>
@@ -262,9 +262,6 @@
     <t>11600</t>
   </si>
   <si>
-    <t>15771</t>
-  </si>
-  <si>
     <t>NH투자증권</t>
   </si>
   <si>
@@ -277,13 +274,13 @@
     <t>신영증권,케이비증권</t>
   </si>
   <si>
+    <t>대신증권</t>
+  </si>
+  <si>
     <t>키움증권</t>
   </si>
   <si>
     <t>한국투자증권</t>
-  </si>
-  <si>
-    <t>대신증권</t>
   </si>
   <si>
     <t>신한투자증권</t>
@@ -693,13 +690,13 @@
         <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
         <v>68</v>
       </c>
       <c r="F2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -713,13 +710,13 @@
         <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -733,13 +730,13 @@
         <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
         <v>69</v>
       </c>
       <c r="F4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -753,13 +750,13 @@
         <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
         <v>70</v>
       </c>
       <c r="F5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -773,13 +770,13 @@
         <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
         <v>71</v>
       </c>
       <c r="F6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -787,19 +784,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -807,19 +804,19 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -827,19 +824,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
         <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -847,19 +844,19 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
         <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F10" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -867,19 +864,19 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="F11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -887,19 +884,19 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
         <v>59</v>
       </c>
       <c r="E12" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="F12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -907,19 +904,19 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
         <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="F13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -927,19 +924,19 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
         <v>61</v>
       </c>
       <c r="E14" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="F14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -947,7 +944,7 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s">
         <v>53</v>
@@ -956,10 +953,10 @@
         <v>62</v>
       </c>
       <c r="E15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F15" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -967,7 +964,7 @@
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
         <v>54</v>
@@ -976,10 +973,10 @@
         <v>63</v>
       </c>
       <c r="E16" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="F16" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -987,7 +984,7 @@
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
         <v>55</v>
@@ -996,10 +993,10 @@
         <v>64</v>
       </c>
       <c r="E17" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="F17" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1016,10 +1013,10 @@
         <v>65</v>
       </c>
       <c r="E18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F18" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1027,19 +1024,19 @@
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F19" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1047,19 +1044,19 @@
         <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D20" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E20" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="F20" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1070,16 +1067,16 @@
         <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
         <v>67</v>
       </c>
       <c r="E21" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="F21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet2.xlsx
+++ b/datasets/sheet2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="90">
   <si>
     <t>종목명</t>
   </si>
@@ -34,9 +34,18 @@
     <t>주간사</t>
   </si>
   <si>
+    <t>신한스팩14호</t>
+  </si>
+  <si>
     <t>루미르</t>
   </si>
   <si>
+    <t>웨이비스</t>
+  </si>
+  <si>
+    <t>에이치이엠파마(구.에이치이엠)</t>
+  </si>
+  <si>
     <t>한켐</t>
   </si>
   <si>
@@ -61,9 +70,6 @@
     <t>아이언디바이스</t>
   </si>
   <si>
-    <t>에이치이엠파마(구.에이치이엠)</t>
-  </si>
-  <si>
     <t>미래에셋비전스팩7호</t>
   </si>
   <si>
@@ -88,10 +94,7 @@
     <t>전진건설로봇(구.전진중공업)(유가)</t>
   </si>
   <si>
-    <t>교보스팩16호</t>
-  </si>
-  <si>
-    <t>넥스트바이오메디컬</t>
+    <t>2024.10.01~10.02</t>
   </si>
   <si>
     <t>2024.09.09~09.13</t>
@@ -115,9 +118,6 @@
     <t>2024.08.30~09.05</t>
   </si>
   <si>
-    <t>2024.08.26~08.30</t>
-  </si>
-  <si>
     <t>2024.08.26~08.27</t>
   </si>
   <si>
@@ -139,24 +139,24 @@
     <t>2024.07.30~08.05</t>
   </si>
   <si>
-    <t>2024.07.29~07.30</t>
-  </si>
-  <si>
-    <t>2024.07.29~08.02</t>
+    <t>2,000~2,000</t>
   </si>
   <si>
     <t>16,500~20,500</t>
   </si>
   <si>
+    <t>11,000~12,500</t>
+  </si>
+  <si>
+    <t>16,400~19,000</t>
+  </si>
+  <si>
     <t>12,500~14,500</t>
   </si>
   <si>
     <t>8,600~9,800</t>
   </si>
   <si>
-    <t>2,000~2,000</t>
-  </si>
-  <si>
     <t>28,000~34,000</t>
   </si>
   <si>
@@ -169,9 +169,6 @@
     <t>4,900~5,700</t>
   </si>
   <si>
-    <t>18,000~21,000</t>
-  </si>
-  <si>
     <t>32,000~40,200</t>
   </si>
   <si>
@@ -190,9 +187,6 @@
     <t>13,800~15,700</t>
   </si>
   <si>
-    <t>24,000~29,000</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -217,18 +211,18 @@
     <t>16500</t>
   </si>
   <si>
-    <t>29000</t>
+    <t>10000</t>
   </si>
   <si>
     <t>49500</t>
   </si>
   <si>
+    <t>11430</t>
+  </si>
+  <si>
     <t>30616</t>
   </si>
   <si>
-    <t>10000</t>
-  </si>
-  <si>
     <t>18480</t>
   </si>
   <si>
@@ -241,9 +235,6 @@
     <t>14700</t>
   </si>
   <si>
-    <t>12546</t>
-  </si>
-  <si>
     <t>78720</t>
   </si>
   <si>
@@ -259,12 +250,15 @@
     <t>50781</t>
   </si>
   <si>
-    <t>11600</t>
+    <t>신한투자증권</t>
   </si>
   <si>
     <t>NH투자증권</t>
   </si>
   <si>
+    <t>대신증권</t>
+  </si>
+  <si>
     <t>신영증권,유진증권</t>
   </si>
   <si>
@@ -274,18 +268,12 @@
     <t>신영증권,케이비증권</t>
   </si>
   <si>
-    <t>대신증권</t>
-  </si>
-  <si>
     <t>키움증권</t>
   </si>
   <si>
     <t>한국투자증권</t>
   </si>
   <si>
-    <t>신한투자증권</t>
-  </si>
-  <si>
     <t>미래에셋증권</t>
   </si>
   <si>
@@ -296,9 +284,6 @@
   </si>
   <si>
     <t>하나증권</t>
-  </si>
-  <si>
-    <t>교보증권</t>
   </si>
 </sst>
 </file>
@@ -687,16 +672,16 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -707,16 +692,16 @@
         <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -727,16 +712,16 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="F4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -747,16 +732,16 @@
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F5" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -764,19 +749,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="F6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -784,19 +769,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="F7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -804,19 +789,19 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F8" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -824,19 +809,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F9" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -844,19 +829,19 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="F10" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -864,19 +849,19 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F11" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -884,19 +869,19 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F12" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -904,19 +889,19 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F13" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -924,16 +909,16 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F14" t="s">
         <v>86</v>
@@ -944,19 +929,19 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F15" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -964,19 +949,19 @@
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E16" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="F16" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -984,19 +969,19 @@
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E17" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F17" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1004,19 +989,19 @@
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E18" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F18" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1024,19 +1009,19 @@
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E19" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F19" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1044,19 +1029,19 @@
         <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E20" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F20" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1064,19 +1049,19 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D21" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E21" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="F21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet2.xlsx
+++ b/datasets/sheet2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="91">
   <si>
     <t>종목명</t>
   </si>
@@ -37,6 +37,9 @@
     <t>신한스팩14호</t>
   </si>
   <si>
+    <t>씨메스</t>
+  </si>
+  <si>
     <t>루미르</t>
   </si>
   <si>
@@ -91,12 +94,12 @@
     <t>케이쓰리아이</t>
   </si>
   <si>
-    <t>전진건설로봇(구.전진중공업)(유가)</t>
-  </si>
-  <si>
     <t>2024.10.01~10.02</t>
   </si>
   <si>
+    <t>2024.09.19~09.25</t>
+  </si>
+  <si>
     <t>2024.09.09~09.13</t>
   </si>
   <si>
@@ -142,6 +145,9 @@
     <t>2,000~2,000</t>
   </si>
   <si>
+    <t>20,000~24,000</t>
+  </si>
+  <si>
     <t>16,500~20,500</t>
   </si>
   <si>
@@ -184,9 +190,6 @@
     <t>12,500~15,500</t>
   </si>
   <si>
-    <t>13,800~15,700</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -208,12 +211,12 @@
     <t>15500</t>
   </si>
   <si>
-    <t>16500</t>
-  </si>
-  <si>
     <t>10000</t>
   </si>
   <si>
+    <t>52000</t>
+  </si>
+  <si>
     <t>49500</t>
   </si>
   <si>
@@ -247,10 +250,10 @@
     <t>21700</t>
   </si>
   <si>
-    <t>50781</t>
-  </si>
-  <si>
     <t>신한투자증권</t>
+  </si>
+  <si>
+    <t>삼성증권,유진투자증권,유안타증권</t>
   </si>
   <si>
     <t>NH투자증권</t>
@@ -672,10 +675,10 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
         <v>65</v>
@@ -692,10 +695,10 @@
         <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
         <v>66</v>
@@ -709,16 +712,16 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="F4" t="s">
         <v>80</v>
@@ -732,16 +735,16 @@
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -749,19 +752,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -769,16 +772,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="F7" t="s">
         <v>82</v>
@@ -792,16 +795,16 @@
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -812,13 +815,13 @@
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F9" t="s">
         <v>83</v>
@@ -829,19 +832,19 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="F10" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -852,16 +855,16 @@
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -872,10 +875,10 @@
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
         <v>71</v>
@@ -892,16 +895,16 @@
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s">
         <v>72</v>
       </c>
       <c r="F13" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -912,16 +915,16 @@
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="F14" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -932,13 +935,13 @@
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D15" t="s">
         <v>58</v>
       </c>
       <c r="E15" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="F15" t="s">
         <v>87</v>
@@ -952,16 +955,16 @@
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
         <v>59</v>
       </c>
       <c r="E16" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="F16" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -972,16 +975,16 @@
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D17" t="s">
         <v>60</v>
       </c>
       <c r="E17" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="F17" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -992,7 +995,7 @@
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
         <v>61</v>
@@ -1001,7 +1004,7 @@
         <v>75</v>
       </c>
       <c r="F18" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1012,16 +1015,16 @@
         <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
         <v>62</v>
       </c>
       <c r="E19" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="F19" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1032,16 +1035,16 @@
         <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
         <v>63</v>
       </c>
       <c r="E20" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F20" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1049,10 +1052,10 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D21" t="s">
         <v>64</v>
@@ -1061,7 +1064,7 @@
         <v>77</v>
       </c>
       <c r="F21" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet2.xlsx
+++ b/datasets/sheet2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="90">
   <si>
     <t>종목명</t>
   </si>
@@ -37,6 +37,9 @@
     <t>신한스팩14호</t>
   </si>
   <si>
+    <t>클로봇</t>
+  </si>
+  <si>
     <t>씨메스</t>
   </si>
   <si>
@@ -91,12 +94,12 @@
     <t>티디에스팜</t>
   </si>
   <si>
-    <t>케이쓰리아이</t>
-  </si>
-  <si>
     <t>2024.10.01~10.02</t>
   </si>
   <si>
+    <t>2024.09.23~09.27</t>
+  </si>
+  <si>
     <t>2024.09.19~09.25</t>
   </si>
   <si>
@@ -139,12 +142,12 @@
     <t>2024.07.31~08.06</t>
   </si>
   <si>
-    <t>2024.07.30~08.05</t>
-  </si>
-  <si>
     <t>2,000~2,000</t>
   </si>
   <si>
+    <t>9,400~10,900</t>
+  </si>
+  <si>
     <t>20,000~24,000</t>
   </si>
   <si>
@@ -187,9 +190,6 @@
     <t>9,500~10,700</t>
   </si>
   <si>
-    <t>12,500~15,500</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -208,12 +208,12 @@
     <t>13000</t>
   </si>
   <si>
-    <t>15500</t>
-  </si>
-  <si>
     <t>10000</t>
   </si>
   <si>
+    <t>28200</t>
+  </si>
+  <si>
     <t>52000</t>
   </si>
   <si>
@@ -247,12 +247,12 @@
     <t>24000</t>
   </si>
   <si>
-    <t>21700</t>
-  </si>
-  <si>
     <t>신한투자증권</t>
   </si>
   <si>
+    <t>미래에셋증권,신영증권</t>
+  </si>
+  <si>
     <t>삼성증권,유진투자증권,유안타증권</t>
   </si>
   <si>
@@ -284,9 +284,6 @@
   </si>
   <si>
     <t>신영증권,유진투자증권</t>
-  </si>
-  <si>
-    <t>하나증권</t>
   </si>
 </sst>
 </file>
@@ -681,10 +678,10 @@
         <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -701,10 +698,10 @@
         <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -721,10 +718,10 @@
         <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -732,7 +729,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
         <v>45</v>
@@ -741,10 +738,10 @@
         <v>58</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="F5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -761,10 +758,10 @@
         <v>58</v>
       </c>
       <c r="E6" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="F6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -772,7 +769,7 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
         <v>47</v>
@@ -781,10 +778,10 @@
         <v>58</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F7" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -792,7 +789,7 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
         <v>48</v>
@@ -801,10 +798,10 @@
         <v>58</v>
       </c>
       <c r="E8" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -815,13 +812,13 @@
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
         <v>58</v>
       </c>
       <c r="E9" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F9" t="s">
         <v>83</v>
@@ -835,16 +832,16 @@
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
         <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -852,7 +849,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
         <v>50</v>
@@ -861,10 +858,10 @@
         <v>58</v>
       </c>
       <c r="E11" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="F11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -875,16 +872,16 @@
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
         <v>58</v>
       </c>
       <c r="E12" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="F12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -895,16 +892,16 @@
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
         <v>58</v>
       </c>
       <c r="E13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -921,10 +918,10 @@
         <v>58</v>
       </c>
       <c r="E14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -935,16 +932,16 @@
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
         <v>58</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="F15" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -955,16 +952,16 @@
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E16" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="F16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -975,16 +972,16 @@
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F17" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -995,16 +992,16 @@
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E18" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="F18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1018,13 +1015,13 @@
         <v>55</v>
       </c>
       <c r="D19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F19" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1038,13 +1035,13 @@
         <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E20" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="F20" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1058,13 +1055,13 @@
         <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E21" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="F21" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet2.xlsx
+++ b/datasets/sheet2.xlsx
@@ -94,7 +94,7 @@
     <t>티디에스팜</t>
   </si>
   <si>
-    <t>2024.10.01~10.02</t>
+    <t>2024.09.26~09.27</t>
   </si>
   <si>
     <t>2024.09.23~09.27</t>

--- a/datasets/sheet2.xlsx
+++ b/datasets/sheet2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="85">
   <si>
     <t>종목명</t>
   </si>
@@ -34,12 +34,27 @@
     <t>주간사</t>
   </si>
   <si>
+    <t>쓰리빌리언</t>
+  </si>
+  <si>
     <t>신한스팩14호</t>
   </si>
   <si>
+    <t>탑런토탈솔루션</t>
+  </si>
+  <si>
+    <t>인스피언</t>
+  </si>
+  <si>
+    <t>한켐</t>
+  </si>
+  <si>
     <t>클로봇</t>
   </si>
   <si>
+    <t>토모큐브</t>
+  </si>
+  <si>
     <t>씨메스</t>
   </si>
   <si>
@@ -52,9 +67,6 @@
     <t>에이치이엠파마(구.에이치이엠)</t>
   </si>
   <si>
-    <t>한켐</t>
-  </si>
-  <si>
     <t>와이제이링크</t>
   </si>
   <si>
@@ -70,9 +82,6 @@
     <t>키움스팩9호</t>
   </si>
   <si>
-    <t>인스피언</t>
-  </si>
-  <si>
     <t>아이언디바이스</t>
   </si>
   <si>
@@ -85,21 +94,21 @@
     <t>대신밸런스스팩18호</t>
   </si>
   <si>
-    <t>이엔셀</t>
-  </si>
-  <si>
-    <t>엠83</t>
-  </si>
-  <si>
-    <t>티디에스팜</t>
+    <t>2024.09.27~10.04</t>
   </si>
   <si>
     <t>2024.09.26~09.27</t>
   </si>
   <si>
+    <t>2024.09.24~09.30</t>
+  </si>
+  <si>
     <t>2024.09.23~09.27</t>
   </si>
   <si>
+    <t>2024.09.20~09.26</t>
+  </si>
+  <si>
     <t>2024.09.19~09.25</t>
   </si>
   <si>
@@ -118,9 +127,6 @@
     <t>2024.09.04~09.05</t>
   </si>
   <si>
-    <t>2024.09.04~09.10</t>
-  </si>
-  <si>
     <t>2024.08.30~09.05</t>
   </si>
   <si>
@@ -133,21 +139,27 @@
     <t>2024.08.05~08.06</t>
   </si>
   <si>
-    <t>2024.08.02~08.08</t>
-  </si>
-  <si>
-    <t>2024.08.01~08.07</t>
-  </si>
-  <si>
-    <t>2024.07.31~08.06</t>
+    <t>4,500~6,500</t>
   </si>
   <si>
     <t>2,000~2,000</t>
   </si>
   <si>
+    <t>12,000~14,000</t>
+  </si>
+  <si>
+    <t>8,000~10,000</t>
+  </si>
+  <si>
+    <t>12,500~14,500</t>
+  </si>
+  <si>
     <t>9,400~10,900</t>
   </si>
   <si>
+    <t>10,900~13,400</t>
+  </si>
+  <si>
     <t>20,000~24,000</t>
   </si>
   <si>
@@ -160,9 +172,6 @@
     <t>16,400~19,000</t>
   </si>
   <si>
-    <t>12,500~14,500</t>
-  </si>
-  <si>
     <t>8,600~9,800</t>
   </si>
   <si>
@@ -172,118 +181,94 @@
     <t>10,000~12,200</t>
   </si>
   <si>
-    <t>8,000~10,000</t>
-  </si>
-  <si>
     <t>4,900~5,700</t>
   </si>
   <si>
     <t>32,000~40,200</t>
   </si>
   <si>
-    <t>13,600~15,300</t>
-  </si>
-  <si>
-    <t>11,000~13,000</t>
-  </si>
-  <si>
-    <t>9,500~10,700</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
+    <t>2000</t>
+  </si>
+  <si>
     <t>32000</t>
   </si>
   <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>15300</t>
-  </si>
-  <si>
-    <t>16000</t>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>28200</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>49500</t>
+  </si>
+  <si>
+    <t>11430</t>
+  </si>
+  <si>
+    <t>30616</t>
+  </si>
+  <si>
+    <t>18480</t>
+  </si>
+  <si>
+    <t>6000</t>
+  </si>
+  <si>
+    <t>14700</t>
+  </si>
+  <si>
+    <t>15900</t>
+  </si>
+  <si>
+    <t>78720</t>
   </si>
   <si>
     <t>13000</t>
   </si>
   <si>
-    <t>10000</t>
-  </si>
-  <si>
-    <t>28200</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>49500</t>
-  </si>
-  <si>
-    <t>11430</t>
-  </si>
-  <si>
-    <t>30616</t>
-  </si>
-  <si>
-    <t>18480</t>
-  </si>
-  <si>
-    <t>6000</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>14700</t>
-  </si>
-  <si>
-    <t>78720</t>
-  </si>
-  <si>
-    <t>23972</t>
-  </si>
-  <si>
-    <t>24000</t>
+    <t>한국투자증권</t>
   </si>
   <si>
     <t>신한투자증권</t>
   </si>
   <si>
+    <t>KB증권</t>
+  </si>
+  <si>
+    <t>신영증권,유진증권</t>
+  </si>
+  <si>
     <t>미래에셋증권,신영증권</t>
   </si>
   <si>
+    <t>대신증권</t>
+  </si>
+  <si>
     <t>삼성증권,유진투자증권,유안타증권</t>
   </si>
   <si>
     <t>NH투자증권</t>
   </si>
   <si>
-    <t>대신증권</t>
-  </si>
-  <si>
-    <t>신영증권,유진증권</t>
-  </si>
-  <si>
-    <t>KB증권</t>
-  </si>
-  <si>
     <t>신영증권,케이비증권</t>
   </si>
   <si>
     <t>키움증권</t>
   </si>
   <si>
-    <t>한국투자증권</t>
-  </si>
-  <si>
     <t>미래에셋증권</t>
   </si>
   <si>
     <t>삼성증권</t>
-  </si>
-  <si>
-    <t>신영증권,유진투자증권</t>
   </si>
 </sst>
 </file>
@@ -672,16 +657,16 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -692,16 +677,16 @@
         <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -712,16 +697,16 @@
         <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -732,16 +717,16 @@
         <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F5" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -752,16 +737,16 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -769,16 +754,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F7" t="s">
         <v>77</v>
@@ -792,16 +777,16 @@
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F8" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -809,19 +794,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F9" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -829,19 +814,19 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
         <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -855,13 +840,13 @@
         <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F11" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -869,19 +854,19 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
         <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F12" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -892,16 +877,16 @@
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F13" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -912,16 +897,16 @@
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="F14" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -935,10 +920,10 @@
         <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E15" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F15" t="s">
         <v>81</v>
@@ -949,19 +934,19 @@
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F16" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -969,19 +954,19 @@
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E17" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -989,19 +974,19 @@
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E18" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F18" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1009,19 +994,19 @@
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="D19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E19" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1029,19 +1014,19 @@
         <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
         <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E20" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F20" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1049,19 +1034,19 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D21" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E21" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="F21" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet2.xlsx
+++ b/datasets/sheet2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="86">
   <si>
     <t>종목명</t>
   </si>
@@ -40,6 +40,9 @@
     <t>신한스팩14호</t>
   </si>
   <si>
+    <t>와이제이링크</t>
+  </si>
+  <si>
     <t>탑런토탈솔루션</t>
   </si>
   <si>
@@ -67,9 +70,6 @@
     <t>에이치이엠파마(구.에이치이엠)</t>
   </si>
   <si>
-    <t>와이제이링크</t>
-  </si>
-  <si>
     <t>KB스팩30호</t>
   </si>
   <si>
@@ -100,6 +100,9 @@
     <t>2024.09.26~09.27</t>
   </si>
   <si>
+    <t>2024.09.25~10.02</t>
+  </si>
+  <si>
     <t>2024.09.24~09.30</t>
   </si>
   <si>
@@ -145,6 +148,9 @@
     <t>2,000~2,000</t>
   </si>
   <si>
+    <t>8,600~9,800</t>
+  </si>
+  <si>
     <t>12,000~14,000</t>
   </si>
   <si>
@@ -172,9 +178,6 @@
     <t>16,400~19,000</t>
   </si>
   <si>
-    <t>8,600~9,800</t>
-  </si>
-  <si>
     <t>28,000~34,000</t>
   </si>
   <si>
@@ -199,6 +202,9 @@
     <t>10000</t>
   </si>
   <si>
+    <t>30616</t>
+  </si>
+  <si>
     <t>18000</t>
   </si>
   <si>
@@ -212,9 +218,6 @@
   </si>
   <si>
     <t>11430</t>
-  </si>
-  <si>
-    <t>30616</t>
   </si>
   <si>
     <t>18480</t>
@@ -657,16 +660,16 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -677,16 +680,16 @@
         <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -697,16 +700,16 @@
         <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -717,16 +720,16 @@
         <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -734,19 +737,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -754,16 +757,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F7" t="s">
         <v>77</v>
@@ -777,13 +780,13 @@
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F8" t="s">
         <v>78</v>
@@ -797,13 +800,13 @@
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F9" t="s">
         <v>79</v>
@@ -817,13 +820,13 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F10" t="s">
         <v>80</v>
@@ -834,19 +837,19 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E11" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="F11" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -857,16 +860,16 @@
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -874,16 +877,16 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F13" t="s">
         <v>75</v>
@@ -894,19 +897,19 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -914,19 +917,19 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -934,19 +937,19 @@
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -954,19 +957,19 @@
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -974,19 +977,19 @@
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -994,19 +997,19 @@
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1014,19 +1017,19 @@
         <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1034,19 +1037,19 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet2.xlsx
+++ b/datasets/sheet2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="87">
   <si>
     <t>종목명</t>
   </si>
@@ -37,12 +37,18 @@
     <t>쓰리빌리언</t>
   </si>
   <si>
+    <t>루미르</t>
+  </si>
+  <si>
     <t>신한스팩14호</t>
   </si>
   <si>
     <t>와이제이링크</t>
   </si>
   <si>
+    <t>셀비온</t>
+  </si>
+  <si>
     <t>탑런토탈솔루션</t>
   </si>
   <si>
@@ -61,9 +67,6 @@
     <t>씨메스</t>
   </si>
   <si>
-    <t>루미르</t>
-  </si>
-  <si>
     <t>웨이비스</t>
   </si>
   <si>
@@ -76,9 +79,6 @@
     <t>제닉스</t>
   </si>
   <si>
-    <t>셀비온</t>
-  </si>
-  <si>
     <t>키움스팩9호</t>
   </si>
   <si>
@@ -97,6 +97,9 @@
     <t>2024.09.27~10.04</t>
   </si>
   <si>
+    <t>2024.09.26~10.04</t>
+  </si>
+  <si>
     <t>2024.09.26~09.27</t>
   </si>
   <si>
@@ -145,12 +148,18 @@
     <t>4,500~6,500</t>
   </si>
   <si>
+    <t>16,500~20,500</t>
+  </si>
+  <si>
     <t>2,000~2,000</t>
   </si>
   <si>
     <t>8,600~9,800</t>
   </si>
   <si>
+    <t>10,000~12,200</t>
+  </si>
+  <si>
     <t>12,000~14,000</t>
   </si>
   <si>
@@ -169,9 +178,6 @@
     <t>20,000~24,000</t>
   </si>
   <si>
-    <t>16,500~20,500</t>
-  </si>
-  <si>
     <t>11,000~12,500</t>
   </si>
   <si>
@@ -181,9 +187,6 @@
     <t>28,000~34,000</t>
   </si>
   <si>
-    <t>10,000~12,200</t>
-  </si>
-  <si>
     <t>4,900~5,700</t>
   </si>
   <si>
@@ -199,6 +202,9 @@
     <t>32000</t>
   </si>
   <si>
+    <t>49500</t>
+  </si>
+  <si>
     <t>10000</t>
   </si>
   <si>
@@ -214,9 +220,6 @@
     <t>52000</t>
   </si>
   <si>
-    <t>49500</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -241,28 +244,28 @@
     <t>한국투자증권</t>
   </si>
   <si>
+    <t>NH투자증권</t>
+  </si>
+  <si>
     <t>신한투자증권</t>
   </si>
   <si>
     <t>KB증권</t>
   </si>
   <si>
+    <t>대신증권</t>
+  </si>
+  <si>
     <t>신영증권,유진증권</t>
   </si>
   <si>
     <t>미래에셋증권,신영증권</t>
   </si>
   <si>
-    <t>대신증권</t>
-  </si>
-  <si>
     <t>삼성증권,유진투자증권,유안타증권</t>
   </si>
   <si>
-    <t>NH투자증권</t>
-  </si>
-  <si>
-    <t>신영증권,케이비증권</t>
+    <t>신영증권,KB증권</t>
   </si>
   <si>
     <t>키움증권</t>
@@ -660,16 +663,16 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -680,16 +683,16 @@
         <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -700,16 +703,16 @@
         <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -720,16 +723,16 @@
         <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -740,16 +743,16 @@
         <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F6" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -760,16 +763,16 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -777,19 +780,19 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -800,16 +803,16 @@
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -817,19 +820,19 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -837,19 +840,19 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -860,16 +863,16 @@
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="F12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -880,16 +883,16 @@
         <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F13" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -900,16 +903,16 @@
         <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E14" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -920,16 +923,16 @@
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -937,19 +940,19 @@
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E16" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="F16" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -957,19 +960,19 @@
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -977,16 +980,16 @@
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F18" t="s">
         <v>79</v>
@@ -997,19 +1000,19 @@
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1017,19 +1020,19 @@
         <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1037,16 +1040,16 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F21" t="s">
         <v>79</v>

--- a/datasets/sheet2.xlsx
+++ b/datasets/sheet2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="89">
   <si>
     <t>종목명</t>
   </si>
@@ -34,6 +34,9 @@
     <t>주간사</t>
   </si>
   <si>
+    <t>더본코리아(유가)</t>
+  </si>
+  <si>
     <t>쓰리빌리언</t>
   </si>
   <si>
@@ -91,7 +94,7 @@
     <t>아이스크림미디어(구.시공미디어)</t>
   </si>
   <si>
-    <t>대신밸런스스팩18호</t>
+    <t>2024.10.15~10.21</t>
   </si>
   <si>
     <t>2024.09.27~10.04</t>
@@ -142,7 +145,7 @@
     <t>2024.08.09~08.16</t>
   </si>
   <si>
-    <t>2024.08.05~08.06</t>
+    <t>23,000~28,000</t>
   </si>
   <si>
     <t>4,500~6,500</t>
@@ -202,6 +205,9 @@
     <t>32000</t>
   </si>
   <si>
+    <t>69000</t>
+  </si>
+  <si>
     <t>49500</t>
   </si>
   <si>
@@ -238,7 +244,7 @@
     <t>78720</t>
   </si>
   <si>
-    <t>13000</t>
+    <t>한국투자증권,NH투자증권</t>
   </si>
   <si>
     <t>한국투자증권</t>
@@ -666,13 +672,13 @@
         <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -686,13 +692,13 @@
         <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -706,13 +712,13 @@
         <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -726,13 +732,13 @@
         <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -746,13 +752,13 @@
         <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -760,19 +766,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
         <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -786,13 +792,13 @@
         <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F8" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -800,19 +806,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
         <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -820,19 +826,19 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
         <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -846,13 +852,13 @@
         <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="F11" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -866,13 +872,13 @@
         <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -886,13 +892,13 @@
         <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F13" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -906,13 +912,13 @@
         <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F14" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -923,16 +929,16 @@
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E15" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -943,16 +949,16 @@
         <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E16" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F16" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -963,16 +969,16 @@
         <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -983,16 +989,16 @@
         <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F18" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1003,16 +1009,16 @@
         <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
         <v>60</v>
       </c>
       <c r="E19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F19" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1023,16 +1029,16 @@
         <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D20" t="s">
         <v>61</v>
       </c>
       <c r="E20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1043,16 +1049,16 @@
         <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F21" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet2.xlsx
+++ b/datasets/sheet2.xlsx
@@ -82,9 +82,6 @@
     <t>제닉스</t>
   </si>
   <si>
-    <t>키움스팩9호</t>
-  </si>
-  <si>
     <t>아이언디바이스</t>
   </si>
   <si>
@@ -94,6 +91,9 @@
     <t>아이스크림미디어(구.시공미디어)</t>
   </si>
   <si>
+    <t>대신밸런스스팩18호</t>
+  </si>
+  <si>
     <t>2024.10.15~10.21</t>
   </si>
   <si>
@@ -133,9 +133,6 @@
     <t>2024.09.05~09.11</t>
   </si>
   <si>
-    <t>2024.09.04~09.05</t>
-  </si>
-  <si>
     <t>2024.08.30~09.05</t>
   </si>
   <si>
@@ -145,6 +142,9 @@
     <t>2024.08.09~08.16</t>
   </si>
   <si>
+    <t>2024.08.05~08.06</t>
+  </si>
+  <si>
     <t>23,000~28,000</t>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>2000</t>
   </si>
   <si>
+    <t>7000</t>
+  </si>
+  <si>
     <t>32000</t>
   </si>
   <si>
@@ -232,10 +235,7 @@
     <t>18480</t>
   </si>
   <si>
-    <t>6000</t>
-  </si>
-  <si>
-    <t>14700</t>
+    <t>21000</t>
   </si>
   <si>
     <t>15900</t>
@@ -244,6 +244,9 @@
     <t>78720</t>
   </si>
   <si>
+    <t>13000</t>
+  </si>
+  <si>
     <t>한국투자증권,NH투자증권</t>
   </si>
   <si>
@@ -272,9 +275,6 @@
   </si>
   <si>
     <t>신영증권,KB증권</t>
-  </si>
-  <si>
-    <t>키움증권</t>
   </si>
   <si>
     <t>미래에셋증권</t>
@@ -675,10 +675,10 @@
         <v>60</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -698,7 +698,7 @@
         <v>60</v>
       </c>
       <c r="F3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -715,10 +715,10 @@
         <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -735,10 +735,10 @@
         <v>60</v>
       </c>
       <c r="E5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -755,10 +755,10 @@
         <v>60</v>
       </c>
       <c r="E6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -778,7 +778,7 @@
         <v>60</v>
       </c>
       <c r="F7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -798,7 +798,7 @@
         <v>60</v>
       </c>
       <c r="F8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -815,10 +815,10 @@
         <v>60</v>
       </c>
       <c r="E9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -838,7 +838,7 @@
         <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -855,10 +855,10 @@
         <v>60</v>
       </c>
       <c r="E11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -878,7 +878,7 @@
         <v>60</v>
       </c>
       <c r="F12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -895,10 +895,10 @@
         <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -918,7 +918,7 @@
         <v>60</v>
       </c>
       <c r="F14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -935,10 +935,10 @@
         <v>60</v>
       </c>
       <c r="E15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -952,13 +952,13 @@
         <v>46</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -975,10 +975,10 @@
         <v>60</v>
       </c>
       <c r="E17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -989,16 +989,16 @@
         <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F18" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1009,16 +1009,16 @@
         <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F19" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1029,16 +1029,16 @@
         <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1049,16 +1049,16 @@
         <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="D21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F21" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet2.xlsx
+++ b/datasets/sheet2.xlsx
@@ -37,6 +37,9 @@
     <t>더본코리아(유가)</t>
   </si>
   <si>
+    <t>씨메스</t>
+  </si>
+  <si>
     <t>쓰리빌리언</t>
   </si>
   <si>
@@ -67,9 +70,6 @@
     <t>토모큐브</t>
   </si>
   <si>
-    <t>씨메스</t>
-  </si>
-  <si>
     <t>웨이비스</t>
   </si>
   <si>
@@ -97,6 +97,9 @@
     <t>2024.10.15~10.21</t>
   </si>
   <si>
+    <t>2024.09.30~10.08</t>
+  </si>
+  <si>
     <t>2024.09.27~10.04</t>
   </si>
   <si>
@@ -118,9 +121,6 @@
     <t>2024.09.20~09.26</t>
   </si>
   <si>
-    <t>2024.09.19~09.25</t>
-  </si>
-  <si>
     <t>2024.09.09~09.13</t>
   </si>
   <si>
@@ -148,6 +148,9 @@
     <t>23,000~28,000</t>
   </si>
   <si>
+    <t>20,000~24,000</t>
+  </si>
+  <si>
     <t>4,500~6,500</t>
   </si>
   <si>
@@ -178,9 +181,6 @@
     <t>10,900~13,400</t>
   </si>
   <si>
-    <t>20,000~24,000</t>
-  </si>
-  <si>
     <t>11,000~12,500</t>
   </si>
   <si>
@@ -211,6 +211,9 @@
     <t>69000</t>
   </si>
   <si>
+    <t>52000</t>
+  </si>
+  <si>
     <t>49500</t>
   </si>
   <si>
@@ -226,9 +229,6 @@
     <t>28200</t>
   </si>
   <si>
-    <t>52000</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -250,6 +250,9 @@
     <t>한국투자증권,NH투자증권</t>
   </si>
   <si>
+    <t>삼성증권,유진투자증권,유안타증권</t>
+  </si>
+  <si>
     <t>한국투자증권</t>
   </si>
   <si>
@@ -269,9 +272,6 @@
   </si>
   <si>
     <t>미래에셋증권,신영증권</t>
-  </si>
-  <si>
-    <t>삼성증권,유진투자증권,유안타증권</t>
   </si>
   <si>
     <t>신영증권,KB증권</t>
@@ -695,7 +695,7 @@
         <v>60</v>
       </c>
       <c r="E3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F3" t="s">
         <v>78</v>
@@ -715,7 +715,7 @@
         <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F4" t="s">
         <v>79</v>
@@ -775,7 +775,7 @@
         <v>60</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F7" t="s">
         <v>82</v>
@@ -786,7 +786,7 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
         <v>49</v>
@@ -798,7 +798,7 @@
         <v>60</v>
       </c>
       <c r="F8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -815,10 +815,10 @@
         <v>60</v>
       </c>
       <c r="E9" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F9" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -826,7 +826,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
         <v>51</v>
@@ -835,10 +835,10 @@
         <v>60</v>
       </c>
       <c r="E10" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="F10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -846,7 +846,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
@@ -855,7 +855,7 @@
         <v>60</v>
       </c>
       <c r="E11" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="F11" t="s">
         <v>84</v>
@@ -875,10 +875,10 @@
         <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F12" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -895,10 +895,10 @@
         <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -918,7 +918,7 @@
         <v>60</v>
       </c>
       <c r="F14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -938,7 +938,7 @@
         <v>71</v>
       </c>
       <c r="F15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -949,16 +949,16 @@
         <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
         <v>61</v>
       </c>
       <c r="E16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -998,7 +998,7 @@
         <v>73</v>
       </c>
       <c r="F18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1009,7 +1009,7 @@
         <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s">
         <v>61</v>
@@ -1049,7 +1049,7 @@
         <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s">
         <v>61</v>
@@ -1058,7 +1058,7 @@
         <v>76</v>
       </c>
       <c r="F21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet2.xlsx
+++ b/datasets/sheet2.xlsx
@@ -37,6 +37,12 @@
     <t>더본코리아(유가)</t>
   </si>
   <si>
+    <t>닷밀</t>
+  </si>
+  <si>
+    <t>웨이비스</t>
+  </si>
+  <si>
     <t>씨메스</t>
   </si>
   <si>
@@ -70,9 +76,6 @@
     <t>토모큐브</t>
   </si>
   <si>
-    <t>웨이비스</t>
-  </si>
-  <si>
     <t>에이치이엠파마(구.에이치이엠)</t>
   </si>
   <si>
@@ -91,12 +94,15 @@
     <t>아이스크림미디어(구.시공미디어)</t>
   </si>
   <si>
-    <t>대신밸런스스팩18호</t>
-  </si>
-  <si>
     <t>2024.10.15~10.21</t>
   </si>
   <si>
+    <t>2024.10.10~10.16</t>
+  </si>
+  <si>
+    <t>2024.10.07~10.14</t>
+  </si>
+  <si>
     <t>2024.09.30~10.08</t>
   </si>
   <si>
@@ -121,9 +127,6 @@
     <t>2024.09.20~09.26</t>
   </si>
   <si>
-    <t>2024.09.09~09.13</t>
-  </si>
-  <si>
     <t>2024.09.06~09.12</t>
   </si>
   <si>
@@ -142,12 +145,15 @@
     <t>2024.08.09~08.16</t>
   </si>
   <si>
-    <t>2024.08.05~08.06</t>
-  </si>
-  <si>
     <t>23,000~28,000</t>
   </si>
   <si>
+    <t>11,000~13,000</t>
+  </si>
+  <si>
+    <t>11,000~12,500</t>
+  </si>
+  <si>
     <t>20,000~24,000</t>
   </si>
   <si>
@@ -181,9 +187,6 @@
     <t>10,900~13,400</t>
   </si>
   <si>
-    <t>11,000~12,500</t>
-  </si>
-  <si>
     <t>16,400~19,000</t>
   </si>
   <si>
@@ -244,12 +247,15 @@
     <t>78720</t>
   </si>
   <si>
-    <t>13000</t>
-  </si>
-  <si>
     <t>한국투자증권,NH투자증권</t>
   </si>
   <si>
+    <t>미래에셋증권</t>
+  </si>
+  <si>
+    <t>대신증권</t>
+  </si>
+  <si>
     <t>삼성증권,유진투자증권,유안타증권</t>
   </si>
   <si>
@@ -265,9 +271,6 @@
     <t>KB증권</t>
   </si>
   <si>
-    <t>대신증권</t>
-  </si>
-  <si>
     <t>신영증권,유진증권</t>
   </si>
   <si>
@@ -275,9 +278,6 @@
   </si>
   <si>
     <t>신영증권,KB증권</t>
-  </si>
-  <si>
-    <t>미래에셋증권</t>
   </si>
   <si>
     <t>삼성증권</t>
@@ -672,10 +672,10 @@
         <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F2" t="s">
         <v>77</v>
@@ -692,10 +692,10 @@
         <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F3" t="s">
         <v>78</v>
@@ -712,10 +712,10 @@
         <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F4" t="s">
         <v>79</v>
@@ -732,7 +732,7 @@
         <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
         <v>66</v>
@@ -752,10 +752,10 @@
         <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F6" t="s">
         <v>81</v>
@@ -772,10 +772,10 @@
         <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F7" t="s">
         <v>82</v>
@@ -792,10 +792,10 @@
         <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E8" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F8" t="s">
         <v>83</v>
@@ -806,19 +806,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
         <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E9" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="F9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -826,16 +826,16 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
         <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E10" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F10" t="s">
         <v>79</v>
@@ -846,16 +846,16 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F11" t="s">
         <v>84</v>
@@ -866,19 +866,19 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
         <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E12" t="s">
         <v>70</v>
       </c>
       <c r="F12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -886,19 +886,19 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
         <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -912,13 +912,13 @@
         <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E14" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="F14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -932,13 +932,13 @@
         <v>56</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="F15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -949,16 +949,16 @@
         <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
         <v>61</v>
       </c>
       <c r="E16" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -969,16 +969,16 @@
         <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E17" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -992,13 +992,13 @@
         <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E18" t="s">
         <v>73</v>
       </c>
       <c r="F18" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1009,16 +1009,16 @@
         <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E19" t="s">
         <v>74</v>
       </c>
       <c r="F19" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1029,16 +1029,16 @@
         <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="D20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E20" t="s">
         <v>75</v>
       </c>
       <c r="F20" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1049,16 +1049,16 @@
         <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E21" t="s">
         <v>76</v>
       </c>
       <c r="F21" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet2.xlsx
+++ b/datasets/sheet2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="87">
   <si>
     <t>종목명</t>
   </si>
@@ -34,15 +34,24 @@
     <t>주간사</t>
   </si>
   <si>
+    <t>위츠</t>
+  </si>
+  <si>
     <t>더본코리아(유가)</t>
   </si>
   <si>
     <t>닷밀</t>
   </si>
   <si>
+    <t>성우</t>
+  </si>
+  <si>
     <t>웨이비스</t>
   </si>
   <si>
+    <t>클로봇</t>
+  </si>
+  <si>
     <t>씨메스</t>
   </si>
   <si>
@@ -70,9 +79,6 @@
     <t>한켐</t>
   </si>
   <si>
-    <t>클로봇</t>
-  </si>
-  <si>
     <t>토모큐브</t>
   </si>
   <si>
@@ -88,10 +94,7 @@
     <t>아이언디바이스</t>
   </si>
   <si>
-    <t>미래에셋비전스팩7호</t>
-  </si>
-  <si>
-    <t>아이스크림미디어(구.시공미디어)</t>
+    <t>2024.10.28~11.01</t>
   </si>
   <si>
     <t>2024.10.15~10.21</t>
@@ -139,10 +142,7 @@
     <t>2024.08.30~09.05</t>
   </si>
   <si>
-    <t>2024.08.26~08.27</t>
-  </si>
-  <si>
-    <t>2024.08.09~08.16</t>
+    <t>5,300~6,400</t>
   </si>
   <si>
     <t>23,000~28,000</t>
@@ -151,9 +151,15 @@
     <t>11,000~13,000</t>
   </si>
   <si>
+    <t>25,000~29,000</t>
+  </si>
+  <si>
     <t>11,000~12,500</t>
   </si>
   <si>
+    <t>9,400~10,900</t>
+  </si>
+  <si>
     <t>20,000~24,000</t>
   </si>
   <si>
@@ -181,9 +187,6 @@
     <t>12,500~14,500</t>
   </si>
   <si>
-    <t>9,400~10,900</t>
-  </si>
-  <si>
     <t>10,900~13,400</t>
   </si>
   <si>
@@ -196,9 +199,6 @@
     <t>4,900~5,700</t>
   </si>
   <si>
-    <t>32,000~40,200</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -208,12 +208,18 @@
     <t>7000</t>
   </si>
   <si>
-    <t>32000</t>
+    <t>15900</t>
   </si>
   <si>
     <t>69000</t>
   </si>
   <si>
+    <t>75000</t>
+  </si>
+  <si>
+    <t>28200</t>
+  </si>
+  <si>
     <t>52000</t>
   </si>
   <si>
@@ -229,9 +235,6 @@
     <t>18000</t>
   </si>
   <si>
-    <t>28200</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -241,10 +244,7 @@
     <t>21000</t>
   </si>
   <si>
-    <t>15900</t>
-  </si>
-  <si>
-    <t>78720</t>
+    <t>신한투자증권</t>
   </si>
   <si>
     <t>한국투자증권,NH투자증권</t>
@@ -253,34 +253,28 @@
     <t>미래에셋증권</t>
   </si>
   <si>
+    <t>한국투자증권</t>
+  </si>
+  <si>
     <t>대신증권</t>
   </si>
   <si>
+    <t>미래에셋증권,신영증권</t>
+  </si>
+  <si>
     <t>삼성증권,유진투자증권,유안타증권</t>
   </si>
   <si>
-    <t>한국투자증권</t>
-  </si>
-  <si>
     <t>NH투자증권</t>
   </si>
   <si>
-    <t>신한투자증권</t>
-  </si>
-  <si>
     <t>KB증권</t>
   </si>
   <si>
     <t>신영증권,유진증권</t>
   </si>
   <si>
-    <t>미래에셋증권,신영증권</t>
-  </si>
-  <si>
     <t>신영증권,KB증권</t>
-  </si>
-  <si>
-    <t>삼성증권</t>
   </si>
 </sst>
 </file>
@@ -669,16 +663,16 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
         <v>61</v>
       </c>
       <c r="E2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -689,16 +683,16 @@
         <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
         <v>61</v>
       </c>
       <c r="E3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -709,7 +703,7 @@
         <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
         <v>61</v>
@@ -718,7 +712,7 @@
         <v>61</v>
       </c>
       <c r="F4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -726,10 +720,10 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
         <v>61</v>
@@ -738,7 +732,7 @@
         <v>66</v>
       </c>
       <c r="F5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -746,10 +740,10 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
         <v>61</v>
@@ -758,7 +752,7 @@
         <v>61</v>
       </c>
       <c r="F6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -766,10 +760,10 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
         <v>61</v>
@@ -778,7 +772,7 @@
         <v>67</v>
       </c>
       <c r="F7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -786,10 +780,10 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
         <v>61</v>
@@ -798,7 +792,7 @@
         <v>68</v>
       </c>
       <c r="F8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -806,19 +800,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
         <v>61</v>
       </c>
       <c r="E9" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F9" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -826,19 +820,19 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
         <v>61</v>
       </c>
       <c r="E10" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F10" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -846,19 +840,19 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
         <v>61</v>
       </c>
       <c r="E11" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="F11" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -866,19 +860,19 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
         <v>61</v>
       </c>
       <c r="E12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -889,7 +883,7 @@
         <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
         <v>61</v>
@@ -898,7 +892,7 @@
         <v>61</v>
       </c>
       <c r="F13" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -909,16 +903,16 @@
         <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
         <v>61</v>
       </c>
       <c r="E14" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="F14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -929,13 +923,13 @@
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s">
         <v>61</v>
       </c>
       <c r="E15" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="F15" t="s">
         <v>79</v>
@@ -946,19 +940,19 @@
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D16" t="s">
         <v>61</v>
       </c>
       <c r="E16" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="F16" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -966,19 +960,19 @@
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E17" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="F17" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -986,7 +980,7 @@
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
         <v>58</v>
@@ -998,7 +992,7 @@
         <v>73</v>
       </c>
       <c r="F18" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1006,19 +1000,19 @@
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E19" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F19" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1026,19 +1020,19 @@
         <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F20" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1046,19 +1040,19 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
         <v>60</v>
       </c>
       <c r="D21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F21" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet2.xlsx
+++ b/datasets/sheet2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="85">
   <si>
     <t>종목명</t>
   </si>
@@ -40,12 +40,24 @@
     <t>더본코리아(유가)</t>
   </si>
   <si>
+    <t>유진스팩11호</t>
+  </si>
+  <si>
+    <t>노머스</t>
+  </si>
+  <si>
     <t>닷밀</t>
   </si>
   <si>
+    <t>탑런토탈솔루션</t>
+  </si>
+  <si>
     <t>성우</t>
   </si>
   <si>
+    <t>케이뱅크(유가)</t>
+  </si>
+  <si>
     <t>웨이비스</t>
   </si>
   <si>
@@ -55,6 +67,9 @@
     <t>씨메스</t>
   </si>
   <si>
+    <t>에이치엔에스하이텍</t>
+  </si>
+  <si>
     <t>쓰리빌리언</t>
   </si>
   <si>
@@ -70,9 +85,6 @@
     <t>셀비온</t>
   </si>
   <si>
-    <t>탑런토탈솔루션</t>
-  </si>
-  <si>
     <t>인스피언</t>
   </si>
   <si>
@@ -82,24 +94,18 @@
     <t>토모큐브</t>
   </si>
   <si>
-    <t>에이치이엠파마(구.에이치이엠)</t>
-  </si>
-  <si>
-    <t>KB스팩30호</t>
-  </si>
-  <si>
-    <t>제닉스</t>
-  </si>
-  <si>
-    <t>아이언디바이스</t>
-  </si>
-  <si>
     <t>2024.10.28~11.01</t>
   </si>
   <si>
     <t>2024.10.15~10.21</t>
   </si>
   <si>
+    <t>2024.10.15~10.16</t>
+  </si>
+  <si>
+    <t>2024.10.11~10.17</t>
+  </si>
+  <si>
     <t>2024.10.10~10.16</t>
   </si>
   <si>
@@ -130,30 +136,30 @@
     <t>2024.09.20~09.26</t>
   </si>
   <si>
-    <t>2024.09.06~09.12</t>
-  </si>
-  <si>
-    <t>2024.09.05~09.06</t>
-  </si>
-  <si>
-    <t>2024.09.05~09.11</t>
-  </si>
-  <si>
-    <t>2024.08.30~09.05</t>
-  </si>
-  <si>
     <t>5,300~6,400</t>
   </si>
   <si>
     <t>23,000~28,000</t>
   </si>
   <si>
+    <t>2,000~2,000</t>
+  </si>
+  <si>
+    <t>27,200~30,200</t>
+  </si>
+  <si>
     <t>11,000~13,000</t>
   </si>
   <si>
+    <t>12,000~14,000</t>
+  </si>
+  <si>
     <t>25,000~29,000</t>
   </si>
   <si>
+    <t>9,500~12,000</t>
+  </si>
+  <si>
     <t>11,000~12,500</t>
   </si>
   <si>
@@ -163,24 +169,21 @@
     <t>20,000~24,000</t>
   </si>
   <si>
+    <t>22,000~26,000</t>
+  </si>
+  <si>
     <t>4,500~6,500</t>
   </si>
   <si>
     <t>16,500~20,500</t>
   </si>
   <si>
-    <t>2,000~2,000</t>
-  </si>
-  <si>
     <t>8,600~9,800</t>
   </si>
   <si>
     <t>10,000~12,200</t>
   </si>
   <si>
-    <t>12,000~14,000</t>
-  </si>
-  <si>
     <t>8,000~10,000</t>
   </si>
   <si>
@@ -190,39 +193,36 @@
     <t>10,900~13,400</t>
   </si>
   <si>
-    <t>16,400~19,000</t>
-  </si>
-  <si>
-    <t>28,000~34,000</t>
-  </si>
-  <si>
-    <t>4,900~5,700</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>7000</t>
-  </si>
-  <si>
     <t>15900</t>
   </si>
   <si>
     <t>69000</t>
   </si>
   <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>30736</t>
+  </si>
+  <si>
     <t>75000</t>
   </si>
   <si>
+    <t>779000</t>
+  </si>
+  <si>
     <t>28200</t>
   </si>
   <si>
     <t>52000</t>
   </si>
   <si>
+    <t>11000</t>
+  </si>
+  <si>
     <t>49500</t>
   </si>
   <si>
@@ -235,28 +235,28 @@
     <t>18000</t>
   </si>
   <si>
-    <t>11430</t>
-  </si>
-  <si>
-    <t>18480</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
     <t>신한투자증권</t>
   </si>
   <si>
     <t>한국투자증권,NH투자증권</t>
   </si>
   <si>
+    <t>유진증권</t>
+  </si>
+  <si>
+    <t>대신증권</t>
+  </si>
+  <si>
     <t>미래에셋증권</t>
   </si>
   <si>
+    <t>KB증권</t>
+  </si>
+  <si>
     <t>한국투자증권</t>
   </si>
   <si>
-    <t>대신증권</t>
+    <t>NH투자증권,KB증권,신한투자증권,키움증권</t>
   </si>
   <si>
     <t>미래에셋증권,신영증권</t>
@@ -268,13 +268,7 @@
     <t>NH투자증권</t>
   </si>
   <si>
-    <t>KB증권</t>
-  </si>
-  <si>
     <t>신영증권,유진증권</t>
-  </si>
-  <si>
-    <t>신영증권,KB증권</t>
   </si>
 </sst>
 </file>
@@ -663,16 +657,16 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -683,16 +677,16 @@
         <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" t="s">
         <v>61</v>
       </c>
-      <c r="E3" t="s">
-        <v>65</v>
-      </c>
       <c r="F3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -703,16 +697,16 @@
         <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -720,19 +714,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -740,19 +734,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -760,19 +754,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -783,16 +777,16 @@
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -800,19 +794,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -820,19 +814,19 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F10" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -840,19 +834,19 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F11" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -860,19 +854,19 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -880,19 +874,19 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -900,19 +894,19 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E14" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F14" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -920,19 +914,19 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F15" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -940,19 +934,19 @@
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E16" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="F16" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -960,19 +954,19 @@
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E17" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F17" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -980,16 +974,16 @@
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E18" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="F18" t="s">
         <v>76</v>
@@ -1000,19 +994,19 @@
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E19" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F19" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1020,19 +1014,19 @@
         <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E20" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="F20" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1040,19 +1034,19 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E21" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="F21" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet2.xlsx
+++ b/datasets/sheet2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="86">
   <si>
     <t>종목명</t>
   </si>
@@ -37,6 +37,9 @@
     <t>위츠</t>
   </si>
   <si>
+    <t>동방메디컬</t>
+  </si>
+  <si>
     <t>더본코리아(유가)</t>
   </si>
   <si>
@@ -91,12 +94,12 @@
     <t>한켐</t>
   </si>
   <si>
-    <t>토모큐브</t>
-  </si>
-  <si>
     <t>2024.10.28~11.01</t>
   </si>
   <si>
+    <t>2024.10.16~10.22</t>
+  </si>
+  <si>
     <t>2024.10.15~10.21</t>
   </si>
   <si>
@@ -133,12 +136,12 @@
     <t>2024.09.23~09.27</t>
   </si>
   <si>
-    <t>2024.09.20~09.26</t>
-  </si>
-  <si>
     <t>5,300~6,400</t>
   </si>
   <si>
+    <t>9,000~10,500</t>
+  </si>
+  <si>
     <t>23,000~28,000</t>
   </si>
   <si>
@@ -190,15 +193,15 @@
     <t>12,500~14,500</t>
   </si>
   <si>
-    <t>10,900~13,400</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
     <t>15900</t>
   </si>
   <si>
+    <t>30609</t>
+  </si>
+  <si>
     <t>69000</t>
   </si>
   <si>
@@ -238,6 +241,9 @@
     <t>신한투자증권</t>
   </si>
   <si>
+    <t>NH투자증권</t>
+  </si>
+  <si>
     <t>한국투자증권,NH투자증권</t>
   </si>
   <si>
@@ -263,9 +269,6 @@
   </si>
   <si>
     <t>삼성증권,유진투자증권,유안타증권</t>
-  </si>
-  <si>
-    <t>NH투자증권</t>
   </si>
   <si>
     <t>신영증권,유진증권</t>
@@ -666,7 +669,7 @@
         <v>60</v>
       </c>
       <c r="F2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -686,7 +689,7 @@
         <v>61</v>
       </c>
       <c r="F3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -706,7 +709,7 @@
         <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -726,7 +729,7 @@
         <v>63</v>
       </c>
       <c r="F5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -743,10 +746,10 @@
         <v>59</v>
       </c>
       <c r="E6" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -754,7 +757,7 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
         <v>45</v>
@@ -766,7 +769,7 @@
         <v>59</v>
       </c>
       <c r="F7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -774,7 +777,7 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -783,10 +786,10 @@
         <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -794,7 +797,7 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
         <v>47</v>
@@ -806,7 +809,7 @@
         <v>65</v>
       </c>
       <c r="F9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -823,10 +826,10 @@
         <v>59</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F10" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -834,7 +837,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
         <v>49</v>
@@ -843,10 +846,10 @@
         <v>59</v>
       </c>
       <c r="E11" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -866,7 +869,7 @@
         <v>67</v>
       </c>
       <c r="F12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -874,7 +877,7 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
         <v>51</v>
@@ -886,7 +889,7 @@
         <v>68</v>
       </c>
       <c r="F13" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -903,7 +906,7 @@
         <v>59</v>
       </c>
       <c r="E14" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F14" t="s">
         <v>79</v>
@@ -923,10 +926,10 @@
         <v>59</v>
       </c>
       <c r="E15" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -937,7 +940,7 @@
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
         <v>59</v>
@@ -946,7 +949,7 @@
         <v>70</v>
       </c>
       <c r="F16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -957,7 +960,7 @@
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D17" t="s">
         <v>59</v>
@@ -966,7 +969,7 @@
         <v>71</v>
       </c>
       <c r="F17" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -983,10 +986,10 @@
         <v>59</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="F18" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1003,10 +1006,10 @@
         <v>59</v>
       </c>
       <c r="E19" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1014,7 +1017,7 @@
         <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
         <v>57</v>
@@ -1023,10 +1026,10 @@
         <v>59</v>
       </c>
       <c r="E20" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="F20" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1046,7 +1049,7 @@
         <v>59</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet2.xlsx
+++ b/datasets/sheet2.xlsx
@@ -37,6 +37,9 @@
     <t>위츠</t>
   </si>
   <si>
+    <t>엠오티</t>
+  </si>
+  <si>
     <t>동방메디컬</t>
   </si>
   <si>
@@ -46,15 +49,21 @@
     <t>유진스팩11호</t>
   </si>
   <si>
+    <t>에이치이엠파마(구.에이치이엠)</t>
+  </si>
+  <si>
+    <t>탑런토탈솔루션</t>
+  </si>
+  <si>
     <t>노머스</t>
   </si>
   <si>
+    <t>에이럭스</t>
+  </si>
+  <si>
     <t>닷밀</t>
   </si>
   <si>
-    <t>탑런토탈솔루션</t>
-  </si>
-  <si>
     <t>성우</t>
   </si>
   <si>
@@ -85,18 +94,12 @@
     <t>와이제이링크</t>
   </si>
   <si>
-    <t>셀비온</t>
-  </si>
-  <si>
-    <t>인스피언</t>
-  </si>
-  <si>
-    <t>한켐</t>
-  </si>
-  <si>
     <t>2024.10.28~11.01</t>
   </si>
   <si>
+    <t>2024.10.17~10.23</t>
+  </si>
+  <si>
     <t>2024.10.16~10.22</t>
   </si>
   <si>
@@ -106,6 +109,9 @@
     <t>2024.10.15~10.16</t>
   </si>
   <si>
+    <t>2024.10.14~10.18</t>
+  </si>
+  <si>
     <t>2024.10.11~10.17</t>
   </si>
   <si>
@@ -130,15 +136,12 @@
     <t>2024.09.25~10.02</t>
   </si>
   <si>
-    <t>2024.09.24~09.30</t>
-  </si>
-  <si>
-    <t>2024.09.23~09.27</t>
-  </si>
-  <si>
     <t>5,300~6,400</t>
   </si>
   <si>
+    <t>12,000~14,000</t>
+  </si>
+  <si>
     <t>9,000~10,500</t>
   </si>
   <si>
@@ -148,15 +151,18 @@
     <t>2,000~2,000</t>
   </si>
   <si>
+    <t>16,400~19,000</t>
+  </si>
+  <si>
     <t>27,200~30,200</t>
   </si>
   <si>
+    <t>11,500~13,500</t>
+  </si>
+  <si>
     <t>11,000~13,000</t>
   </si>
   <si>
-    <t>12,000~14,000</t>
-  </si>
-  <si>
     <t>25,000~29,000</t>
   </si>
   <si>
@@ -184,21 +190,15 @@
     <t>8,600~9,800</t>
   </si>
   <si>
-    <t>10,000~12,200</t>
-  </si>
-  <si>
-    <t>8,000~10,000</t>
-  </si>
-  <si>
-    <t>12,500~14,500</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
     <t>15900</t>
   </si>
   <si>
+    <t>21000</t>
+  </si>
+  <si>
     <t>30609</t>
   </si>
   <si>
@@ -208,9 +208,15 @@
     <t>9000</t>
   </si>
   <si>
+    <t>11430</t>
+  </si>
+  <si>
     <t>30736</t>
   </si>
   <si>
+    <t>17250</t>
+  </si>
+  <si>
     <t>75000</t>
   </si>
   <si>
@@ -235,12 +241,12 @@
     <t>30616</t>
   </si>
   <si>
-    <t>18000</t>
-  </si>
-  <si>
     <t>신한투자증권</t>
   </si>
   <si>
+    <t>한국투자증권</t>
+  </si>
+  <si>
     <t>NH투자증권</t>
   </si>
   <si>
@@ -250,18 +256,15 @@
     <t>유진증권</t>
   </si>
   <si>
+    <t>KB증권</t>
+  </si>
+  <si>
     <t>대신증권</t>
   </si>
   <si>
     <t>미래에셋증권</t>
   </si>
   <si>
-    <t>KB증권</t>
-  </si>
-  <si>
-    <t>한국투자증권</t>
-  </si>
-  <si>
     <t>NH투자증권,KB증권,신한투자증권,키움증권</t>
   </si>
   <si>
@@ -269,9 +272,6 @@
   </si>
   <si>
     <t>삼성증권,유진투자증권,유안타증권</t>
-  </si>
-  <si>
-    <t>신영증권,유진증권</t>
   </si>
 </sst>
 </file>
@@ -663,13 +663,13 @@
         <v>40</v>
       </c>
       <c r="D2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" t="s">
         <v>59</v>
       </c>
-      <c r="E2" t="s">
-        <v>60</v>
-      </c>
       <c r="F2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -683,13 +683,13 @@
         <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -703,13 +703,13 @@
         <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -723,13 +723,13 @@
         <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -743,13 +743,13 @@
         <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -763,13 +763,13 @@
         <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -780,13 +780,13 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F8" t="s">
         <v>80</v>
@@ -797,13 +797,13 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
         <v>65</v>
@@ -817,19 +817,19 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
         <v>66</v>
       </c>
       <c r="F10" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -837,19 +837,19 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F11" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -857,19 +857,19 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
         <v>67</v>
       </c>
       <c r="F12" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -880,16 +880,16 @@
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
       </c>
       <c r="F13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -897,19 +897,19 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -920,16 +920,16 @@
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -940,16 +940,16 @@
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E16" t="s">
         <v>70</v>
       </c>
       <c r="F16" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -957,19 +957,19 @@
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E17" t="s">
         <v>71</v>
       </c>
       <c r="F17" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -977,19 +977,19 @@
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
         <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E18" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="F18" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -997,19 +997,19 @@
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
         <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E19" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="F19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1017,19 +1017,19 @@
         <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E20" t="s">
         <v>73</v>
       </c>
       <c r="F20" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1040,16 +1040,16 @@
         <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E21" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="F21" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet2.xlsx
+++ b/datasets/sheet2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="85">
   <si>
     <t>종목명</t>
   </si>
@@ -49,6 +49,9 @@
     <t>유진스팩11호</t>
   </si>
   <si>
+    <t>미트박스글로벌</t>
+  </si>
+  <si>
     <t>에이치이엠파마(구.에이치이엠)</t>
   </si>
   <si>
@@ -91,9 +94,6 @@
     <t>신한스팩14호</t>
   </si>
   <si>
-    <t>와이제이링크</t>
-  </si>
-  <si>
     <t>2024.10.28~11.01</t>
   </si>
   <si>
@@ -133,9 +133,6 @@
     <t>2024.09.26~09.27</t>
   </si>
   <si>
-    <t>2024.09.25~10.02</t>
-  </si>
-  <si>
     <t>5,300~6,400</t>
   </si>
   <si>
@@ -151,6 +148,9 @@
     <t>2,000~2,000</t>
   </si>
   <si>
+    <t>23,000~28,500</t>
+  </si>
+  <si>
     <t>16,400~19,000</t>
   </si>
   <si>
@@ -187,9 +187,6 @@
     <t>16,500~20,500</t>
   </si>
   <si>
-    <t>8,600~9,800</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -208,6 +205,9 @@
     <t>9000</t>
   </si>
   <si>
+    <t>23000</t>
+  </si>
+  <si>
     <t>11430</t>
   </si>
   <si>
@@ -238,9 +238,6 @@
     <t>10000</t>
   </si>
   <si>
-    <t>30616</t>
-  </si>
-  <si>
     <t>신한투자증권</t>
   </si>
   <si>
@@ -256,13 +253,13 @@
     <t>유진증권</t>
   </si>
   <si>
+    <t>미래에셋증권</t>
+  </si>
+  <si>
     <t>KB증권</t>
   </si>
   <si>
     <t>대신증권</t>
-  </si>
-  <si>
-    <t>미래에셋증권</t>
   </si>
   <si>
     <t>NH투자증권,KB증권,신한투자증권,키움증권</t>
@@ -660,16 +657,16 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" t="s">
         <v>58</v>
       </c>
-      <c r="E2" t="s">
-        <v>59</v>
-      </c>
       <c r="F2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -680,16 +677,16 @@
         <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -700,16 +697,16 @@
         <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -720,16 +717,16 @@
         <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -740,16 +737,16 @@
         <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -757,19 +754,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F7" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -780,16 +777,16 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F8" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -797,19 +794,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -820,16 +817,16 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F10" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -837,19 +834,19 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F11" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -860,16 +857,16 @@
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="F12" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -880,16 +877,16 @@
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F13" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -897,19 +894,19 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -920,16 +917,16 @@
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E15" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="F15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -937,19 +934,19 @@
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -960,16 +957,16 @@
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F17" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -977,19 +974,19 @@
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E18" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="F18" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -997,19 +994,19 @@
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E19" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="F19" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1017,19 +1014,19 @@
         <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1037,19 +1034,19 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E21" t="s">
+        <v>73</v>
+      </c>
+      <c r="F21" t="s">
         <v>74</v>
-      </c>
-      <c r="F21" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/sheet2.xlsx
+++ b/datasets/sheet2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="84">
   <si>
     <t>종목명</t>
   </si>
@@ -37,6 +37,9 @@
     <t>위츠</t>
   </si>
   <si>
+    <t>토모큐브</t>
+  </si>
+  <si>
     <t>엠오티</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>미트박스글로벌</t>
   </si>
   <si>
+    <t>에어레인</t>
+  </si>
+  <si>
     <t>에이치이엠파마(구.에이치이엠)</t>
   </si>
   <si>
@@ -88,12 +94,6 @@
     <t>쓰리빌리언</t>
   </si>
   <si>
-    <t>루미르</t>
-  </si>
-  <si>
-    <t>신한스팩14호</t>
-  </si>
-  <si>
     <t>2024.10.28~11.01</t>
   </si>
   <si>
@@ -127,15 +127,12 @@
     <t>2024.09.27~10.04</t>
   </si>
   <si>
-    <t>2024.09.26~10.04</t>
-  </si>
-  <si>
-    <t>2024.09.26~09.27</t>
-  </si>
-  <si>
     <t>5,300~6,400</t>
   </si>
   <si>
+    <t>10,900~13,400</t>
+  </si>
+  <si>
     <t>12,000~14,000</t>
   </si>
   <si>
@@ -151,6 +148,9 @@
     <t>23,000~28,500</t>
   </si>
   <si>
+    <t>16,000~18,500</t>
+  </si>
+  <si>
     <t>16,400~19,000</t>
   </si>
   <si>
@@ -184,9 +184,6 @@
     <t>4,500~6,500</t>
   </si>
   <si>
-    <t>16,500~20,500</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -208,6 +205,9 @@
     <t>23000</t>
   </si>
   <si>
+    <t>19200</t>
+  </si>
+  <si>
     <t>11430</t>
   </si>
   <si>
@@ -232,15 +232,12 @@
     <t>11000</t>
   </si>
   <si>
-    <t>49500</t>
-  </si>
-  <si>
-    <t>10000</t>
-  </si>
-  <si>
     <t>신한투자증권</t>
   </si>
   <si>
+    <t>대신증권</t>
+  </si>
+  <si>
     <t>한국투자증권</t>
   </si>
   <si>
@@ -256,10 +253,10 @@
     <t>미래에셋증권</t>
   </si>
   <si>
+    <t>신영증권</t>
+  </si>
+  <si>
     <t>KB증권</t>
-  </si>
-  <si>
-    <t>대신증권</t>
   </si>
   <si>
     <t>NH투자증권,KB증권,신한투자증권,키움증권</t>
@@ -657,16 +654,16 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" t="s">
         <v>57</v>
       </c>
-      <c r="E2" t="s">
-        <v>58</v>
-      </c>
       <c r="F2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -677,16 +674,16 @@
         <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -694,19 +691,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -714,19 +711,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -734,19 +731,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -754,19 +751,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -774,19 +771,19 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -794,19 +791,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -814,19 +811,19 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -834,19 +831,19 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F11" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -854,19 +851,19 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F12" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -874,19 +871,19 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -897,16 +894,16 @@
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="F14" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -914,19 +911,19 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="F15" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -934,19 +931,19 @@
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -954,19 +951,19 @@
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E17" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="F17" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -974,19 +971,19 @@
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F18" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -994,19 +991,19 @@
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="F19" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1014,19 +1011,19 @@
         <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F20" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1034,16 +1031,16 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="F21" t="s">
         <v>74</v>

--- a/datasets/sheet2.xlsx
+++ b/datasets/sheet2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="83">
   <si>
     <t>종목명</t>
   </si>
@@ -37,6 +37,9 @@
     <t>위츠</t>
   </si>
   <si>
+    <t>신한스팩15호</t>
+  </si>
+  <si>
     <t>토모큐브</t>
   </si>
   <si>
@@ -91,12 +94,12 @@
     <t>에이치엔에스하이텍</t>
   </si>
   <si>
-    <t>쓰리빌리언</t>
-  </si>
-  <si>
     <t>2024.10.28~11.01</t>
   </si>
   <si>
+    <t>2024.10.28~10.29</t>
+  </si>
+  <si>
     <t>2024.10.17~10.23</t>
   </si>
   <si>
@@ -124,12 +127,12 @@
     <t>2024.09.30~10.08</t>
   </si>
   <si>
-    <t>2024.09.27~10.04</t>
-  </si>
-  <si>
     <t>5,300~6,400</t>
   </si>
   <si>
+    <t>2,000~2,000</t>
+  </si>
+  <si>
     <t>10,900~13,400</t>
   </si>
   <si>
@@ -142,9 +145,6 @@
     <t>23,000~28,000</t>
   </si>
   <si>
-    <t>2,000~2,000</t>
-  </si>
-  <si>
     <t>23,000~28,500</t>
   </si>
   <si>
@@ -179,9 +179,6 @@
   </si>
   <si>
     <t>22,000~26,000</t>
-  </si>
-  <si>
-    <t>4,500~6,500</t>
   </si>
   <si>
     <t>-</t>
@@ -657,13 +654,13 @@
         <v>37</v>
       </c>
       <c r="D2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" t="s">
         <v>56</v>
       </c>
-      <c r="E2" t="s">
-        <v>57</v>
-      </c>
       <c r="F2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -677,13 +674,13 @@
         <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -691,19 +688,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
         <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -717,13 +714,13 @@
         <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -737,13 +734,13 @@
         <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -757,13 +754,13 @@
         <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -771,19 +768,19 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -791,19 +788,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -811,19 +808,19 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -831,19 +828,19 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F11" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -854,16 +851,16 @@
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -871,19 +868,19 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -894,16 +891,16 @@
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="F14" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -911,19 +908,19 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="F15" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -931,19 +928,19 @@
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F16" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -954,16 +951,16 @@
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E17" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="F17" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -971,19 +968,19 @@
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E18" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="F18" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -994,16 +991,16 @@
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1011,19 +1008,19 @@
         <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E20" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F20" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1034,16 +1031,16 @@
         <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="F21" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
